--- a/public/templates/examples/A-066-BackupScheduleMediaInventory-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-066-BackupScheduleMediaInventory-EXAMPLE-S.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backup Schedule" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Media Inventory" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Backup Schedule'!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -260,6 +265,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -938,19 +946,15 @@
           <t>County IT</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="D13" s="26">
+        <v>46062</v>
+      </c>
+      <c r="E13" s="26">
+        <v>46069</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Overdue</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-03-01)</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1031,6 @@
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1039,7 +1042,6 @@
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="13">
         <f>COUNTIF(F11:F20,"Overdue")</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1050,8 +1052,7 @@
       </c>
       <c r="B25" s="24" t="n"/>
       <c r="C25" s="13">
-        <f>COUNTIF(E11:E20,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(E11:E20,"&lt;"&amp;DATE(2026,3,1))</f>
       </c>
     </row>
     <row r="26"/>
@@ -1065,7 +1066,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="9" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="34.7" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scheduled backup fails or an item is overdue, County IT is alerted, and the failure is recorded and escalated to the Director within one business day.</t>
@@ -1202,10 +1203,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
+      <c r="B46" s="26">
+        <v>46068</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
@@ -1221,8 +1220,8 @@
       <c r="F46" s="12" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -1254,14 +1253,8 @@
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F11:F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"On track,Due soon,Overdue,Complete"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1294,7 +1287,7 @@
       <c r="A2" s="9" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Media / Target ID</t>
@@ -1326,7 +1319,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34.7" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
           <t>EXT-DRIVE-1</t>
@@ -1358,7 +1351,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34.7" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
           <t>CLOUD-A</t>
@@ -1475,8 +1468,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>